--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-pss10-score-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-pss10-score-observation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6088" uniqueCount="678">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6088" uniqueCount="679">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T07:28:06+00:00</t>
+    <t>2026-10-21T09:39:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1518,6 +1518,10 @@
   <si>
     <t xml:space="preserve">obs-3
 </t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
     <t>OBX-7</t>
@@ -8687,7 +8691,7 @@
         <v>480</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>105</v>
+        <v>481</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>21</v>
@@ -8696,10 +8700,10 @@
         <v>21</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>21</v>
@@ -8710,10 +8714,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8739,10 +8743,10 @@
         <v>477</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8793,7 +8797,7 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8805,7 +8809,7 @@
         <v>480</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>105</v>
+        <v>481</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>21</v>
@@ -8814,10 +8818,10 @@
         <v>21</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>21</v>
@@ -8828,10 +8832,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8857,16 +8861,16 @@
         <v>182</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>21</v>
@@ -8894,10 +8898,10 @@
         <v>117</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>21</v>
@@ -8915,7 +8919,7 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8933,10 +8937,10 @@
         <v>21</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>414</v>
@@ -8950,10 +8954,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8979,16 +8983,16 @@
         <v>182</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>21</v>
@@ -9016,10 +9020,10 @@
         <v>270</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>21</v>
@@ -9037,7 +9041,7 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -9055,10 +9059,10 @@
         <v>21</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>414</v>
@@ -9072,10 +9076,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9098,17 +9102,17 @@
         <v>21</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>21</v>
@@ -9157,7 +9161,7 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -9181,7 +9185,7 @@
         <v>21</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>21</v>
@@ -9192,10 +9196,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9221,10 +9225,10 @@
         <v>160</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -9275,7 +9279,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -9296,10 +9300,10 @@
         <v>21</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>21</v>
@@ -9310,10 +9314,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9336,16 +9340,16 @@
         <v>94</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9395,7 +9399,7 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -9416,10 +9420,10 @@
         <v>21</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>21</v>
@@ -9430,10 +9434,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9456,16 +9460,16 @@
         <v>94</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9515,7 +9519,7 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9536,10 +9540,10 @@
         <v>21</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>21</v>
@@ -9550,10 +9554,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9561,10 +9565,10 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>21</v>
@@ -9579,16 +9583,16 @@
         <v>461</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>21</v>
@@ -9625,7 +9629,7 @@
         <v>21</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AC59" s="2"/>
       <c r="AD59" t="s" s="2">
@@ -9635,7 +9639,7 @@
         <v>314</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9656,10 +9660,10 @@
         <v>21</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>21</v>
@@ -9670,10 +9674,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9788,10 +9792,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9908,10 +9912,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10030,10 +10034,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10059,13 +10063,13 @@
         <v>182</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="O63" t="s" s="2">
         <v>268</v>
@@ -10117,7 +10121,7 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>93</v>
@@ -10135,7 +10139,7 @@
         <v>21</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>275</v>
@@ -10152,10 +10156,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10178,16 +10182,16 @@
         <v>94</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="M64" t="s" s="2">
         <v>342</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="O64" t="s" s="2">
         <v>344</v>
@@ -10239,7 +10243,7 @@
         <v>21</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -10257,7 +10261,7 @@
         <v>21</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>347</v>
@@ -10274,10 +10278,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10303,13 +10307,13 @@
         <v>182</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="O65" t="s" s="2">
         <v>399</v>
@@ -10361,7 +10365,7 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -10396,10 +10400,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10483,7 +10487,7 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10518,10 +10522,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10547,10 +10551,10 @@
         <v>21</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="N67" t="s" s="2">
         <v>464</v>
@@ -10605,7 +10609,7 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10640,13 +10644,13 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D68" t="s" s="2">
         <v>21</v>
@@ -10671,16 +10675,16 @@
         <v>461</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>21</v>
@@ -10729,7 +10733,7 @@
         <v>21</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10750,10 +10754,10 @@
         <v>21</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>21</v>
@@ -10764,10 +10768,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10882,10 +10886,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11002,10 +11006,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11124,10 +11128,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11153,13 +11157,13 @@
         <v>182</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="O72" t="s" s="2">
         <v>268</v>
@@ -11172,7 +11176,7 @@
         <v>21</v>
       </c>
       <c r="S72" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="T72" t="s" s="2">
         <v>21</v>
@@ -11211,7 +11215,7 @@
         <v>21</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>93</v>
@@ -11229,7 +11233,7 @@
         <v>21</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>275</v>
@@ -11246,10 +11250,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11275,13 +11279,13 @@
         <v>182</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="M73" t="s" s="2">
         <v>342</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="O73" t="s" s="2">
         <v>344</v>
@@ -11313,7 +11317,7 @@
       </c>
       <c r="Y73" s="2"/>
       <c r="Z73" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>21</v>
@@ -11331,7 +11335,7 @@
         <v>21</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -11349,7 +11353,7 @@
         <v>21</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>347</v>
@@ -11366,10 +11370,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11395,13 +11399,13 @@
         <v>182</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="O74" t="s" s="2">
         <v>399</v>
@@ -11453,7 +11457,7 @@
         <v>21</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11488,10 +11492,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11575,7 +11579,7 @@
         <v>21</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11610,10 +11614,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11639,10 +11643,10 @@
         <v>83</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="N76" t="s" s="2">
         <v>464</v>
@@ -11697,7 +11701,7 @@
         <v>21</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11732,13 +11736,13 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="D77" t="s" s="2">
         <v>21</v>
@@ -11763,16 +11767,16 @@
         <v>461</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>21</v>
@@ -11821,7 +11825,7 @@
         <v>21</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11842,10 +11846,10 @@
         <v>21</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>21</v>
@@ -11856,10 +11860,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11974,10 +11978,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12094,10 +12098,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12216,10 +12220,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12245,13 +12249,13 @@
         <v>182</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="O81" t="s" s="2">
         <v>268</v>
@@ -12264,7 +12268,7 @@
         <v>21</v>
       </c>
       <c r="S81" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="T81" t="s" s="2">
         <v>21</v>
@@ -12303,7 +12307,7 @@
         <v>21</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>93</v>
@@ -12321,7 +12325,7 @@
         <v>21</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>275</v>
@@ -12338,10 +12342,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12367,13 +12371,13 @@
         <v>182</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="M82" t="s" s="2">
         <v>342</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="O82" t="s" s="2">
         <v>344</v>
@@ -12405,7 +12409,7 @@
       </c>
       <c r="Y82" s="2"/>
       <c r="Z82" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>21</v>
@@ -12423,7 +12427,7 @@
         <v>21</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -12441,7 +12445,7 @@
         <v>21</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>347</v>
@@ -12458,10 +12462,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12487,13 +12491,13 @@
         <v>182</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="O83" t="s" s="2">
         <v>399</v>
@@ -12545,7 +12549,7 @@
         <v>21</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -12580,10 +12584,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12667,7 +12671,7 @@
         <v>21</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -12702,10 +12706,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12731,10 +12735,10 @@
         <v>83</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="N85" t="s" s="2">
         <v>464</v>
@@ -12789,7 +12793,7 @@
         <v>21</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12824,13 +12828,13 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="D86" t="s" s="2">
         <v>21</v>
@@ -12855,16 +12859,16 @@
         <v>461</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>21</v>
@@ -12913,7 +12917,7 @@
         <v>21</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -12934,10 +12938,10 @@
         <v>21</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>21</v>
@@ -12948,10 +12952,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13066,10 +13070,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13186,10 +13190,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13308,10 +13312,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13337,13 +13341,13 @@
         <v>182</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="O90" t="s" s="2">
         <v>268</v>
@@ -13356,7 +13360,7 @@
         <v>21</v>
       </c>
       <c r="S90" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="T90" t="s" s="2">
         <v>21</v>
@@ -13395,7 +13399,7 @@
         <v>21</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>93</v>
@@ -13413,7 +13417,7 @@
         <v>21</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>275</v>
@@ -13430,10 +13434,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13459,13 +13463,13 @@
         <v>182</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="M91" t="s" s="2">
         <v>342</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="O91" t="s" s="2">
         <v>344</v>
@@ -13497,7 +13501,7 @@
       </c>
       <c r="Y91" s="2"/>
       <c r="Z91" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>21</v>
@@ -13515,7 +13519,7 @@
         <v>21</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -13533,7 +13537,7 @@
         <v>21</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>347</v>
@@ -13550,10 +13554,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13579,13 +13583,13 @@
         <v>182</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="O92" t="s" s="2">
         <v>399</v>
@@ -13637,7 +13641,7 @@
         <v>21</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -13672,10 +13676,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13759,7 +13763,7 @@
         <v>21</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -13794,10 +13798,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13823,10 +13827,10 @@
         <v>83</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="N94" t="s" s="2">
         <v>464</v>
@@ -13881,7 +13885,7 @@
         <v>21</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -13916,13 +13920,13 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="D95" t="s" s="2">
         <v>21</v>
@@ -13947,16 +13951,16 @@
         <v>461</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>21</v>
@@ -14005,7 +14009,7 @@
         <v>21</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>81</v>
@@ -14026,10 +14030,10 @@
         <v>21</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>21</v>
@@ -14040,10 +14044,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14158,10 +14162,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14278,10 +14282,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14400,10 +14404,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14429,13 +14433,13 @@
         <v>182</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="O99" t="s" s="2">
         <v>268</v>
@@ -14448,7 +14452,7 @@
         <v>21</v>
       </c>
       <c r="S99" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="T99" t="s" s="2">
         <v>21</v>
@@ -14487,7 +14491,7 @@
         <v>21</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>93</v>
@@ -14505,7 +14509,7 @@
         <v>21</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>275</v>
@@ -14522,10 +14526,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14551,13 +14555,13 @@
         <v>182</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="M100" t="s" s="2">
         <v>342</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="O100" t="s" s="2">
         <v>344</v>
@@ -14589,7 +14593,7 @@
       </c>
       <c r="Y100" s="2"/>
       <c r="Z100" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>21</v>
@@ -14607,7 +14611,7 @@
         <v>21</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>81</v>
@@ -14625,7 +14629,7 @@
         <v>21</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>347</v>
@@ -14642,10 +14646,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14671,13 +14675,13 @@
         <v>182</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="O101" t="s" s="2">
         <v>399</v>
@@ -14729,7 +14733,7 @@
         <v>21</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>81</v>
@@ -14764,10 +14768,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14851,7 +14855,7 @@
         <v>21</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>81</v>
@@ -14886,10 +14890,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14915,10 +14919,10 @@
         <v>83</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="N103" t="s" s="2">
         <v>464</v>
@@ -14973,7 +14977,7 @@
         <v>21</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>81</v>
@@ -15008,13 +15012,13 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="D104" t="s" s="2">
         <v>21</v>
@@ -15039,16 +15043,16 @@
         <v>461</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>21</v>
@@ -15097,7 +15101,7 @@
         <v>21</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>81</v>
@@ -15118,10 +15122,10 @@
         <v>21</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>21</v>
@@ -15132,10 +15136,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15250,10 +15254,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15370,10 +15374,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15492,10 +15496,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15521,13 +15525,13 @@
         <v>182</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="O108" t="s" s="2">
         <v>268</v>
@@ -15540,7 +15544,7 @@
         <v>21</v>
       </c>
       <c r="S108" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="T108" t="s" s="2">
         <v>21</v>
@@ -15579,7 +15583,7 @@
         <v>21</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>93</v>
@@ -15597,7 +15601,7 @@
         <v>21</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>275</v>
@@ -15614,10 +15618,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15643,13 +15647,13 @@
         <v>182</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="M109" t="s" s="2">
         <v>342</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="O109" t="s" s="2">
         <v>344</v>
@@ -15681,7 +15685,7 @@
       </c>
       <c r="Y109" s="2"/>
       <c r="Z109" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>21</v>
@@ -15699,7 +15703,7 @@
         <v>21</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>81</v>
@@ -15717,7 +15721,7 @@
         <v>21</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>347</v>
@@ -15734,10 +15738,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15763,13 +15767,13 @@
         <v>182</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="O110" t="s" s="2">
         <v>399</v>
@@ -15821,7 +15825,7 @@
         <v>21</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>81</v>
@@ -15856,10 +15860,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15943,7 +15947,7 @@
         <v>21</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>81</v>
@@ -15978,10 +15982,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16007,10 +16011,10 @@
         <v>83</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="N112" t="s" s="2">
         <v>464</v>
@@ -16065,7 +16069,7 @@
         <v>21</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>81</v>
@@ -16100,13 +16104,13 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="D113" t="s" s="2">
         <v>21</v>
@@ -16131,16 +16135,16 @@
         <v>461</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>21</v>
@@ -16189,7 +16193,7 @@
         <v>21</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>81</v>
@@ -16210,10 +16214,10 @@
         <v>21</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>21</v>
@@ -16224,10 +16228,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16342,10 +16346,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16462,10 +16466,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16584,10 +16588,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16613,13 +16617,13 @@
         <v>182</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="O117" t="s" s="2">
         <v>268</v>
@@ -16632,7 +16636,7 @@
         <v>21</v>
       </c>
       <c r="S117" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="T117" t="s" s="2">
         <v>21</v>
@@ -16671,7 +16675,7 @@
         <v>21</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>93</v>
@@ -16689,7 +16693,7 @@
         <v>21</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AM117" t="s" s="2">
         <v>275</v>
@@ -16706,10 +16710,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16735,13 +16739,13 @@
         <v>182</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="M118" t="s" s="2">
         <v>342</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="O118" t="s" s="2">
         <v>344</v>
@@ -16773,7 +16777,7 @@
       </c>
       <c r="Y118" s="2"/>
       <c r="Z118" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AA118" t="s" s="2">
         <v>21</v>
@@ -16791,7 +16795,7 @@
         <v>21</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>81</v>
@@ -16809,7 +16813,7 @@
         <v>21</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AM118" t="s" s="2">
         <v>347</v>
@@ -16826,10 +16830,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16855,13 +16859,13 @@
         <v>182</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="O119" t="s" s="2">
         <v>399</v>
@@ -16913,7 +16917,7 @@
         <v>21</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>81</v>
@@ -16948,10 +16952,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17035,7 +17039,7 @@
         <v>21</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>81</v>
@@ -17070,10 +17074,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17099,10 +17103,10 @@
         <v>83</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="N121" t="s" s="2">
         <v>464</v>
@@ -17157,7 +17161,7 @@
         <v>21</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>81</v>
@@ -17192,13 +17196,13 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C122" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="D122" t="s" s="2">
         <v>21</v>
@@ -17223,16 +17227,16 @@
         <v>461</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="O122" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>21</v>
@@ -17281,7 +17285,7 @@
         <v>21</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>81</v>
@@ -17302,10 +17306,10 @@
         <v>21</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AO122" t="s" s="2">
         <v>21</v>
@@ -17316,10 +17320,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17434,10 +17438,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17554,10 +17558,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17676,10 +17680,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17705,13 +17709,13 @@
         <v>182</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="O126" t="s" s="2">
         <v>268</v>
@@ -17724,7 +17728,7 @@
         <v>21</v>
       </c>
       <c r="S126" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="T126" t="s" s="2">
         <v>21</v>
@@ -17763,7 +17767,7 @@
         <v>21</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>93</v>
@@ -17781,7 +17785,7 @@
         <v>21</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AM126" t="s" s="2">
         <v>275</v>
@@ -17798,10 +17802,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17827,13 +17831,13 @@
         <v>182</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="M127" t="s" s="2">
         <v>342</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="O127" t="s" s="2">
         <v>344</v>
@@ -17865,7 +17869,7 @@
       </c>
       <c r="Y127" s="2"/>
       <c r="Z127" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AA127" t="s" s="2">
         <v>21</v>
@@ -17883,7 +17887,7 @@
         <v>21</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>81</v>
@@ -17901,7 +17905,7 @@
         <v>21</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AM127" t="s" s="2">
         <v>347</v>
@@ -17918,10 +17922,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17947,13 +17951,13 @@
         <v>182</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="O128" t="s" s="2">
         <v>399</v>
@@ -18005,7 +18009,7 @@
         <v>21</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>81</v>
@@ -18040,10 +18044,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18127,7 +18131,7 @@
         <v>21</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>81</v>
@@ -18162,10 +18166,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18191,10 +18195,10 @@
         <v>83</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="N130" t="s" s="2">
         <v>464</v>
@@ -18249,7 +18253,7 @@
         <v>21</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>81</v>
@@ -18284,13 +18288,13 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C131" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="D131" t="s" s="2">
         <v>21</v>
@@ -18315,16 +18319,16 @@
         <v>461</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>21</v>
@@ -18373,7 +18377,7 @@
         <v>21</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>81</v>
@@ -18394,10 +18398,10 @@
         <v>21</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AN131" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AO131" t="s" s="2">
         <v>21</v>
@@ -18408,10 +18412,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18526,10 +18530,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18646,10 +18650,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18768,10 +18772,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18797,13 +18801,13 @@
         <v>182</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="O135" t="s" s="2">
         <v>268</v>
@@ -18816,7 +18820,7 @@
         <v>21</v>
       </c>
       <c r="S135" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="T135" t="s" s="2">
         <v>21</v>
@@ -18855,7 +18859,7 @@
         <v>21</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>93</v>
@@ -18873,7 +18877,7 @@
         <v>21</v>
       </c>
       <c r="AL135" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AM135" t="s" s="2">
         <v>275</v>
@@ -18890,10 +18894,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18919,13 +18923,13 @@
         <v>182</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="M136" t="s" s="2">
         <v>342</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="O136" t="s" s="2">
         <v>344</v>
@@ -18957,7 +18961,7 @@
       </c>
       <c r="Y136" s="2"/>
       <c r="Z136" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AA136" t="s" s="2">
         <v>21</v>
@@ -18975,7 +18979,7 @@
         <v>21</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>81</v>
@@ -18993,7 +18997,7 @@
         <v>21</v>
       </c>
       <c r="AL136" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AM136" t="s" s="2">
         <v>347</v>
@@ -19010,10 +19014,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -19039,13 +19043,13 @@
         <v>182</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="O137" t="s" s="2">
         <v>399</v>
@@ -19097,7 +19101,7 @@
         <v>21</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>81</v>
@@ -19132,10 +19136,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19219,7 +19223,7 @@
         <v>21</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>81</v>
@@ -19254,10 +19258,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19283,10 +19287,10 @@
         <v>83</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="N139" t="s" s="2">
         <v>464</v>
@@ -19341,7 +19345,7 @@
         <v>21</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>81</v>
@@ -19376,13 +19380,13 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C140" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="D140" t="s" s="2">
         <v>21</v>
@@ -19407,16 +19411,16 @@
         <v>461</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="O140" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>21</v>
@@ -19465,7 +19469,7 @@
         <v>21</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>81</v>
@@ -19486,10 +19490,10 @@
         <v>21</v>
       </c>
       <c r="AM140" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AN140" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AO140" t="s" s="2">
         <v>21</v>
@@ -19500,10 +19504,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19618,10 +19622,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19738,10 +19742,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19860,10 +19864,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19889,13 +19893,13 @@
         <v>182</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="O144" t="s" s="2">
         <v>268</v>
@@ -19908,7 +19912,7 @@
         <v>21</v>
       </c>
       <c r="S144" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="T144" t="s" s="2">
         <v>21</v>
@@ -19947,7 +19951,7 @@
         <v>21</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>93</v>
@@ -19965,7 +19969,7 @@
         <v>21</v>
       </c>
       <c r="AL144" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AM144" t="s" s="2">
         <v>275</v>
@@ -19982,10 +19986,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -20011,13 +20015,13 @@
         <v>182</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="M145" t="s" s="2">
         <v>342</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="O145" t="s" s="2">
         <v>344</v>
@@ -20049,7 +20053,7 @@
       </c>
       <c r="Y145" s="2"/>
       <c r="Z145" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AA145" t="s" s="2">
         <v>21</v>
@@ -20067,7 +20071,7 @@
         <v>21</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>81</v>
@@ -20085,7 +20089,7 @@
         <v>21</v>
       </c>
       <c r="AL145" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AM145" t="s" s="2">
         <v>347</v>
@@ -20102,10 +20106,10 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -20131,13 +20135,13 @@
         <v>182</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="O146" t="s" s="2">
         <v>399</v>
@@ -20189,7 +20193,7 @@
         <v>21</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>81</v>
@@ -20224,10 +20228,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -20311,7 +20315,7 @@
         <v>21</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>81</v>
@@ -20346,10 +20350,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20375,10 +20379,10 @@
         <v>83</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="N148" t="s" s="2">
         <v>464</v>
@@ -20433,7 +20437,7 @@
         <v>21</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>81</v>
@@ -20468,13 +20472,13 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C149" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="D149" t="s" s="2">
         <v>21</v>
@@ -20499,16 +20503,16 @@
         <v>461</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="O149" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>21</v>
@@ -20557,7 +20561,7 @@
         <v>21</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>81</v>
@@ -20578,10 +20582,10 @@
         <v>21</v>
       </c>
       <c r="AM149" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AN149" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AO149" t="s" s="2">
         <v>21</v>
@@ -20592,10 +20596,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20710,10 +20714,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20830,10 +20834,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20952,10 +20956,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -20981,13 +20985,13 @@
         <v>182</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="N153" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="O153" t="s" s="2">
         <v>268</v>
@@ -21000,7 +21004,7 @@
         <v>21</v>
       </c>
       <c r="S153" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="T153" t="s" s="2">
         <v>21</v>
@@ -21039,7 +21043,7 @@
         <v>21</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>93</v>
@@ -21057,7 +21061,7 @@
         <v>21</v>
       </c>
       <c r="AL153" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AM153" t="s" s="2">
         <v>275</v>
@@ -21074,10 +21078,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21103,13 +21107,13 @@
         <v>182</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="M154" t="s" s="2">
         <v>342</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="O154" t="s" s="2">
         <v>344</v>
@@ -21141,7 +21145,7 @@
       </c>
       <c r="Y154" s="2"/>
       <c r="Z154" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AA154" t="s" s="2">
         <v>21</v>
@@ -21159,7 +21163,7 @@
         <v>21</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>81</v>
@@ -21177,7 +21181,7 @@
         <v>21</v>
       </c>
       <c r="AL154" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AM154" t="s" s="2">
         <v>347</v>
@@ -21194,10 +21198,10 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21223,13 +21227,13 @@
         <v>182</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="O155" t="s" s="2">
         <v>399</v>
@@ -21281,7 +21285,7 @@
         <v>21</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>81</v>
@@ -21316,10 +21320,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21403,7 +21407,7 @@
         <v>21</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>81</v>
@@ -21438,10 +21442,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21467,10 +21471,10 @@
         <v>83</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="N157" t="s" s="2">
         <v>464</v>
@@ -21525,7 +21529,7 @@
         <v>21</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>81</v>
